--- a/data/form_generation/input/templates/frameB_MRC.xlsx
+++ b/data/form_generation/input/templates/frameB_MRC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E17744B-E9DD-4D65-82BA-0CA409102B07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526F314D-82DE-4736-B2D5-7E675BC3D509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="53">
   <si>
     <t>基本情報1</t>
   </si>
@@ -186,6 +186,10 @@
   <si>
     <t>実施内容
 ※解体機器や解体物量に関する情報はここには記載せず、下部の表に記載を行う</t>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>40,000円</t>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -399,7 +403,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -472,6 +476,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -479,7 +505,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -492,15 +518,6 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -532,12 +549,6 @@
     <xf numFmtId="0" fontId="3" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -547,73 +558,100 @@
     <xf numFmtId="0" fontId="3" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
@@ -926,7 +964,7 @@
     <col min="2" max="2" width="15.44140625" customWidth="1"/>
     <col min="3" max="3" width="16.109375" customWidth="1"/>
     <col min="4" max="4" width="18.21875" customWidth="1"/>
-    <col min="5" max="5" width="20.33203125" customWidth="1"/>
+    <col min="5" max="5" width="13.109375" customWidth="1"/>
     <col min="6" max="14" width="14" customWidth="1"/>
     <col min="15" max="15" width="16.109375" customWidth="1"/>
   </cols>
@@ -940,395 +978,395 @@
       </c>
     </row>
     <row r="4" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="23"/>
-      <c r="E4" s="8" t="s">
+      <c r="C4" s="18"/>
+      <c r="E4" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="55"/>
+      <c r="G4" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="36"/>
-      <c r="H4" s="36"/>
-      <c r="I4" s="36"/>
-      <c r="J4" s="36"/>
-      <c r="K4" s="31" t="s">
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="9" t="s">
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="23"/>
-      <c r="E5" s="7" t="s">
+      <c r="C5" s="18"/>
+      <c r="E5" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="51"/>
+      <c r="G5" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="38"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
-      <c r="K5" s="29" t="s">
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
+      <c r="K5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="11"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="8"/>
     </row>
     <row r="6" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="24"/>
-      <c r="E6" s="6" t="s">
+      <c r="C6" s="19"/>
+      <c r="E6" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="27"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="29" t="s">
+      <c r="F6" s="49"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="11"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="8"/>
     </row>
     <row r="7" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="23"/>
-      <c r="E7" s="6" t="s">
+      <c r="C7" s="18"/>
+      <c r="E7" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="47"/>
+      <c r="F7" s="49"/>
       <c r="G7" s="48"/>
       <c r="H7" s="48"/>
       <c r="I7" s="48"/>
       <c r="J7" s="48"/>
-      <c r="K7" s="29" t="s">
+      <c r="K7" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30"/>
-      <c r="N7" s="30"/>
-      <c r="O7" s="11"/>
-    </row>
-    <row r="8" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="B8" s="22" t="s">
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="8"/>
+    </row>
+    <row r="8" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="23"/>
-      <c r="E8" s="6" t="s">
+      <c r="C8" s="18"/>
+      <c r="E8" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="37" t="s">
+      <c r="F8" s="49"/>
+      <c r="G8" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="29" t="s">
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
+      <c r="K8" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="11"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="8"/>
     </row>
     <row r="9" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="27"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34"/>
-      <c r="N9" s="34"/>
-      <c r="O9" s="11"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="47"/>
+      <c r="H9" s="47"/>
+      <c r="I9" s="47"/>
+      <c r="J9" s="47"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="30"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="30"/>
+      <c r="O9" s="8"/>
     </row>
     <row r="10" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="27"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="28"/>
-      <c r="J10" s="28"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="34"/>
-      <c r="M10" s="34"/>
-      <c r="N10" s="34"/>
-      <c r="O10" s="11"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="29"/>
+      <c r="L10" s="30"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="30"/>
+      <c r="O10" s="8"/>
     </row>
     <row r="11" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="27"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="28"/>
-      <c r="J11" s="28"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34"/>
-      <c r="N11" s="34"/>
-      <c r="O11" s="11"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="30"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="30"/>
+      <c r="O11" s="8"/>
     </row>
     <row r="12" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="27"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="28"/>
-      <c r="I12" s="28"/>
-      <c r="J12" s="28"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="11"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="30"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="30"/>
+      <c r="O12" s="8"/>
     </row>
     <row r="13" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="27"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="28"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="11"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="30"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="30"/>
+      <c r="O13" s="8"/>
     </row>
     <row r="14" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="27"/>
-      <c r="G14" s="28"/>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="29" t="s">
+      <c r="F14" s="51"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="L14" s="30"/>
-      <c r="M14" s="30"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="11"/>
+      <c r="L14" s="34"/>
+      <c r="M14" s="34"/>
+      <c r="N14" s="34"/>
+      <c r="O14" s="8"/>
     </row>
     <row r="15" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="27"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
-      <c r="K15" s="29" t="s">
+      <c r="F15" s="51"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="L15" s="30"/>
-      <c r="M15" s="30"/>
-      <c r="N15" s="30"/>
-      <c r="O15" s="11"/>
+      <c r="L15" s="34"/>
+      <c r="M15" s="34"/>
+      <c r="N15" s="34"/>
+      <c r="O15" s="8"/>
     </row>
     <row r="16" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="50" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="27"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="29" t="s">
+      <c r="F16" s="51"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="47"/>
+      <c r="K16" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="30"/>
-      <c r="O16" s="11"/>
+      <c r="L16" s="34"/>
+      <c r="M16" s="34"/>
+      <c r="N16" s="34"/>
+      <c r="O16" s="8"/>
     </row>
     <row r="17" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="50" t="s">
         <v>29</v>
       </c>
-      <c r="F17" s="27"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="29" t="s">
+      <c r="F17" s="51"/>
+      <c r="G17" s="47"/>
+      <c r="H17" s="47"/>
+      <c r="I17" s="47"/>
+      <c r="J17" s="47"/>
+      <c r="K17" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30"/>
-      <c r="O17" s="11"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="8"/>
     </row>
     <row r="18" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="37" t="s">
+      <c r="F18" s="51"/>
+      <c r="G18" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="H18" s="46"/>
+      <c r="I18" s="46"/>
+      <c r="J18" s="46"/>
+      <c r="K18" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="L18" s="30"/>
-      <c r="M18" s="30"/>
-      <c r="N18" s="30"/>
-      <c r="O18" s="12" t="s">
+      <c r="L18" s="34"/>
+      <c r="M18" s="34"/>
+      <c r="N18" s="34"/>
+      <c r="O18" s="9" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="19" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="37" t="s">
+      <c r="F19" s="51"/>
+      <c r="G19" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="29" t="s">
+      <c r="H19" s="46"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="46"/>
+      <c r="K19" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="L19" s="30"/>
-      <c r="M19" s="30"/>
-      <c r="N19" s="30"/>
-      <c r="O19" s="13" t="s">
+      <c r="L19" s="34"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="10" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="20" spans="2:15" ht="15" x14ac:dyDescent="0.2">
       <c r="E20" s="4"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="42"/>
-      <c r="H20" s="42"/>
-      <c r="I20" s="42"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="41"/>
-      <c r="L20" s="42"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="42"/>
-      <c r="O20" s="10"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="44"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="40"/>
+      <c r="O20" s="7"/>
     </row>
     <row r="21" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E21" s="8" t="s">
+      <c r="E21" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="F21" s="45"/>
+      <c r="G21" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="31" t="s">
+      <c r="H21" s="45"/>
+      <c r="I21" s="45"/>
+      <c r="J21" s="45"/>
+      <c r="K21" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="L21" s="32"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="32"/>
+      <c r="L21" s="38"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
     </row>
     <row r="22" spans="2:15" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E22" s="20" t="s">
+      <c r="E22" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="39"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="40"/>
-      <c r="M22" s="40"/>
-      <c r="N22" s="40"/>
+      <c r="F22" s="56"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="57"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="36"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
     </row>
     <row r="23" spans="2:15" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="F23" s="39"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="39"/>
-      <c r="L23" s="40"/>
-      <c r="M23" s="40"/>
-      <c r="N23" s="40"/>
+      <c r="F23" s="56"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
+      <c r="J23" s="57"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="36"/>
+      <c r="M23" s="36"/>
+      <c r="N23" s="36"/>
     </row>
     <row r="24" spans="2:15" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E24" s="21" t="s">
+      <c r="E24" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="54"/>
-      <c r="G24" s="55"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="55"/>
-      <c r="J24" s="55"/>
-      <c r="K24" s="54"/>
-      <c r="L24" s="55"/>
-      <c r="M24" s="55"/>
-      <c r="N24" s="55"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="59"/>
+      <c r="J24" s="59"/>
+      <c r="K24" s="27"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="28"/>
+      <c r="N24" s="28"/>
     </row>
     <row r="25" spans="2:15" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E25" s="21" t="s">
+      <c r="E25" s="58" t="s">
         <v>39</v>
       </c>
-      <c r="F25" s="54"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="55"/>
-      <c r="I25" s="55"/>
-      <c r="J25" s="55"/>
-      <c r="K25" s="54"/>
-      <c r="L25" s="55"/>
-      <c r="M25" s="55"/>
-      <c r="N25" s="55"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="59"/>
+      <c r="J25" s="59"/>
+      <c r="K25" s="27"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
     </row>
     <row r="26" spans="2:15" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="52" t="s">
+      <c r="B26" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="53"/>
+      <c r="C26" s="26"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
@@ -1342,40 +1380,40 @@
       <c r="N26" s="1"/>
     </row>
     <row r="27" spans="2:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="25" t="s">
+      <c r="B27" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="C27" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="25" t="s">
+      <c r="D27" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="E27" s="25" t="s">
+      <c r="E27" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="F27" s="25" t="s">
+      <c r="F27" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="G27" s="25" t="s">
+      <c r="G27" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="H27" s="26"/>
-      <c r="I27" s="26"/>
-      <c r="J27" s="26"/>
-      <c r="K27" s="44" t="s">
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="L27" s="45"/>
-      <c r="M27" s="45"/>
-      <c r="N27" s="46"/>
+      <c r="L27" s="42"/>
+      <c r="M27" s="42"/>
+      <c r="N27" s="43"/>
     </row>
     <row r="28" spans="2:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="26"/>
-      <c r="C28" s="26"/>
-      <c r="D28" s="26"/>
-      <c r="E28" s="26"/>
-      <c r="F28" s="26"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
       <c r="G28" s="5" t="s">
         <v>46</v>
       </c>
@@ -1388,223 +1426,228 @@
       <c r="J28" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="K28" s="9" t="s">
+      <c r="K28" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="L28" s="9" t="s">
+      <c r="L28" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="M28" s="9" t="s">
+      <c r="M28" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="N28" s="9" t="s">
+      <c r="N28" s="6" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="29" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="B29" s="49" t="s">
+      <c r="B29" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C29" s="50"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="51"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="16">
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="13">
         <v>0</v>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="13">
         <v>0</v>
       </c>
-      <c r="J29" s="16">
+      <c r="J29" s="13">
         <v>0</v>
       </c>
-      <c r="K29" s="19"/>
-      <c r="L29" s="17">
+      <c r="K29" s="16"/>
+      <c r="L29" s="14">
         <v>0</v>
       </c>
-      <c r="M29" s="17">
+      <c r="M29" s="14">
         <v>0</v>
       </c>
-      <c r="N29" s="17">
+      <c r="N29" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="15"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-      <c r="N30" s="15"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
     </row>
     <row r="31" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="15"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-      <c r="N31" s="15"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
     </row>
     <row r="32" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="15"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-      <c r="N32" s="15"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
     </row>
     <row r="33" spans="2:14" ht="15" x14ac:dyDescent="0.2">
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="15"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="12"/>
+      <c r="N33" s="12"/>
     </row>
     <row r="34" spans="2:14" ht="15" x14ac:dyDescent="0.2">
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
-      <c r="K34" s="15"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="15"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+      <c r="N34" s="12"/>
     </row>
     <row r="35" spans="2:14" ht="15" x14ac:dyDescent="0.2">
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="15"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="12"/>
+      <c r="N35" s="12"/>
     </row>
     <row r="36" spans="2:14" ht="15" x14ac:dyDescent="0.2">
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="15"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="15"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
     </row>
     <row r="37" spans="2:14" ht="15" x14ac:dyDescent="0.2">
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="15"/>
-      <c r="L37" s="15"/>
-      <c r="M37" s="15"/>
-      <c r="N37" s="15"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="12"/>
+      <c r="M37" s="12"/>
+      <c r="N37" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="53">
+  <mergeCells count="58">
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="G25:J25"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="K14:N14"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="K13:N13"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="K7:N7"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="K19:N19"/>
+    <mergeCell ref="F20:J20"/>
+    <mergeCell ref="K23:N23"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="K20:N20"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="K22:N22"/>
     <mergeCell ref="B29:F29"/>
     <mergeCell ref="B26:C26"/>
-    <mergeCell ref="F25:J25"/>
     <mergeCell ref="K12:N12"/>
     <mergeCell ref="D27:D28"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="K25:N25"/>
-    <mergeCell ref="F13:J13"/>
     <mergeCell ref="K16:N16"/>
-    <mergeCell ref="F19:J19"/>
     <mergeCell ref="K24:N24"/>
     <mergeCell ref="K15:N15"/>
     <mergeCell ref="E27:E28"/>
     <mergeCell ref="G27:J27"/>
-    <mergeCell ref="F24:J24"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="F22:J22"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="F9:J9"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="F6:J6"/>
-    <mergeCell ref="K21:N21"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="K20:N20"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="K22:N22"/>
-    <mergeCell ref="F7:J7"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="K19:N19"/>
-    <mergeCell ref="F20:J20"/>
-    <mergeCell ref="F21:J21"/>
-    <mergeCell ref="K23:N23"/>
-    <mergeCell ref="F18:J18"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="K14:N14"/>
-    <mergeCell ref="K4:N4"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="K13:N13"/>
-    <mergeCell ref="F4:J4"/>
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="F5:J5"/>
-    <mergeCell ref="K7:N7"/>
-    <mergeCell ref="F23:J23"/>
-    <mergeCell ref="F8:J8"/>
-    <mergeCell ref="K10:N10"/>
-    <mergeCell ref="F14:J14"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/form_generation/input/templates/frameB_MRC.xlsx
+++ b/data/form_generation/input/templates/frameB_MRC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{526F314D-82DE-4736-B2D5-7E675BC3D509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE564D4A-F6AA-4CE3-BA58-E9EC16BE5E90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -505,7 +505,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -558,35 +558,36 @@
     <xf numFmtId="0" fontId="3" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -595,16 +596,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -614,42 +620,68 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -982,22 +1014,22 @@
         <v>2</v>
       </c>
       <c r="C4" s="18"/>
-      <c r="E4" s="54" t="s">
+      <c r="E4" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="55"/>
-      <c r="G4" s="52" t="s">
+      <c r="F4" s="28"/>
+      <c r="G4" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="37" t="s">
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
       <c r="O4" s="6" t="s">
         <v>6</v>
       </c>
@@ -1007,22 +1039,22 @@
         <v>7</v>
       </c>
       <c r="C5" s="18"/>
-      <c r="E5" s="50" t="s">
+      <c r="E5" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="51"/>
-      <c r="G5" s="21" t="s">
+      <c r="F5" s="25"/>
+      <c r="G5" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
-      <c r="K5" s="33" t="s">
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34"/>
-      <c r="N5" s="34"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="2:15" ht="15" x14ac:dyDescent="0.2">
@@ -1030,20 +1062,20 @@
         <v>10</v>
       </c>
       <c r="C6" s="19"/>
-      <c r="E6" s="49" t="s">
+      <c r="E6" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="49"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="33" t="s">
+      <c r="F6" s="29"/>
+      <c r="G6" s="65"/>
+      <c r="H6" s="66"/>
+      <c r="I6" s="66"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="L6" s="34"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="33"/>
       <c r="O6" s="8"/>
     </row>
     <row r="7" spans="2:15" ht="15" x14ac:dyDescent="0.2">
@@ -1051,20 +1083,20 @@
         <v>13</v>
       </c>
       <c r="C7" s="18"/>
-      <c r="E7" s="49" t="s">
+      <c r="E7" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="49"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="33" t="s">
+      <c r="F7" s="29"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="64"/>
+      <c r="K7" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="L7" s="34"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="34"/>
+      <c r="L7" s="33"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
       <c r="O7" s="8"/>
     </row>
     <row r="8" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -1072,301 +1104,301 @@
         <v>16</v>
       </c>
       <c r="C8" s="18"/>
-      <c r="E8" s="49" t="s">
+      <c r="E8" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="49"/>
-      <c r="G8" s="21" t="s">
+      <c r="F8" s="29"/>
+      <c r="G8" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="H8" s="46"/>
-      <c r="I8" s="46"/>
-      <c r="J8" s="46"/>
-      <c r="K8" s="33" t="s">
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="58"/>
+      <c r="K8" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
+      <c r="L8" s="33"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="33"/>
       <c r="O8" s="8"/>
     </row>
     <row r="9" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E9" s="49" t="s">
+      <c r="E9" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="F9" s="49"/>
-      <c r="G9" s="47"/>
-      <c r="H9" s="47"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="47"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="60"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="61"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="37"/>
       <c r="O9" s="8"/>
     </row>
     <row r="10" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E10" s="50" t="s">
+      <c r="E10" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="51"/>
-      <c r="G10" s="47"/>
-      <c r="H10" s="47"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="60"/>
+      <c r="I10" s="60"/>
+      <c r="J10" s="61"/>
+      <c r="K10" s="36"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="37"/>
+      <c r="N10" s="37"/>
       <c r="O10" s="8"/>
     </row>
     <row r="11" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E11" s="50" t="s">
+      <c r="E11" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="F11" s="51"/>
-      <c r="G11" s="47"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="47"/>
-      <c r="J11" s="47"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="60"/>
+      <c r="I11" s="60"/>
+      <c r="J11" s="61"/>
+      <c r="K11" s="36"/>
+      <c r="L11" s="37"/>
+      <c r="M11" s="37"/>
+      <c r="N11" s="37"/>
       <c r="O11" s="8"/>
     </row>
     <row r="12" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E12" s="50" t="s">
+      <c r="E12" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="51"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="47"/>
-      <c r="I12" s="47"/>
-      <c r="J12" s="47"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="30"/>
-      <c r="M12" s="30"/>
-      <c r="N12" s="30"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="60"/>
+      <c r="J12" s="61"/>
+      <c r="K12" s="36"/>
+      <c r="L12" s="37"/>
+      <c r="M12" s="37"/>
+      <c r="N12" s="37"/>
       <c r="O12" s="8"/>
     </row>
     <row r="13" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E13" s="50" t="s">
+      <c r="E13" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="51"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="47"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="30"/>
-      <c r="M13" s="30"/>
-      <c r="N13" s="30"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="60"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="36"/>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
+      <c r="N13" s="37"/>
       <c r="O13" s="8"/>
     </row>
     <row r="14" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E14" s="50" t="s">
+      <c r="E14" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="F14" s="51"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="I14" s="47"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="33" t="s">
+      <c r="F14" s="25"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="60"/>
+      <c r="I14" s="60"/>
+      <c r="J14" s="61"/>
+      <c r="K14" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="34"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
       <c r="O14" s="8"/>
     </row>
     <row r="15" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E15" s="50" t="s">
+      <c r="E15" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="51"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="33" t="s">
+      <c r="F15" s="25"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="60"/>
+      <c r="I15" s="60"/>
+      <c r="J15" s="61"/>
+      <c r="K15" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
-      <c r="N15" s="34"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="33"/>
+      <c r="N15" s="33"/>
       <c r="O15" s="8"/>
     </row>
     <row r="16" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E16" s="50" t="s">
+      <c r="E16" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="51"/>
-      <c r="G16" s="47"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="47"/>
-      <c r="J16" s="47"/>
-      <c r="K16" s="33" t="s">
+      <c r="F16" s="25"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="60"/>
+      <c r="I16" s="60"/>
+      <c r="J16" s="61"/>
+      <c r="K16" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="L16" s="34"/>
-      <c r="M16" s="34"/>
-      <c r="N16" s="34"/>
+      <c r="L16" s="33"/>
+      <c r="M16" s="33"/>
+      <c r="N16" s="33"/>
       <c r="O16" s="8"/>
     </row>
     <row r="17" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E17" s="50" t="s">
+      <c r="E17" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="F17" s="51"/>
-      <c r="G17" s="47"/>
-      <c r="H17" s="47"/>
-      <c r="I17" s="47"/>
-      <c r="J17" s="47"/>
-      <c r="K17" s="33" t="s">
+      <c r="F17" s="25"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="33"/>
       <c r="O17" s="8"/>
     </row>
     <row r="18" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E18" s="50" t="s">
+      <c r="E18" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="51"/>
-      <c r="G18" s="21" t="s">
+      <c r="F18" s="25"/>
+      <c r="G18" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="H18" s="46"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="46"/>
-      <c r="K18" s="33" t="s">
+      <c r="H18" s="57"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="58"/>
+      <c r="K18" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="34"/>
+      <c r="L18" s="33"/>
+      <c r="M18" s="33"/>
+      <c r="N18" s="33"/>
       <c r="O18" s="9" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="19" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E19" s="50" t="s">
+      <c r="E19" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="51"/>
-      <c r="G19" s="21" t="s">
+      <c r="F19" s="25"/>
+      <c r="G19" s="56" t="s">
         <v>33</v>
       </c>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="33" t="s">
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="58"/>
+      <c r="K19" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="33"/>
+      <c r="N19" s="33"/>
       <c r="O19" s="10" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="20" spans="2:15" ht="15" x14ac:dyDescent="0.2">
       <c r="E20" s="4"/>
-      <c r="F20" s="39"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="40"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="44"/>
-      <c r="K20" s="39"/>
-      <c r="L20" s="40"/>
-      <c r="M20" s="40"/>
-      <c r="N20" s="40"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="39"/>
+      <c r="H20" s="39"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="38"/>
+      <c r="L20" s="39"/>
+      <c r="M20" s="39"/>
+      <c r="N20" s="39"/>
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="E21" s="45" t="s">
+      <c r="E21" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45" t="s">
+      <c r="F21" s="21"/>
+      <c r="G21" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="H21" s="45"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="45"/>
-      <c r="K21" s="37" t="s">
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="L21" s="38"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
     </row>
     <row r="22" spans="2:15" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E22" s="56" t="s">
+      <c r="E22" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="F22" s="56"/>
-      <c r="G22" s="57"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="57"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="41"/>
+      <c r="L22" s="42"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="42"/>
     </row>
     <row r="23" spans="2:15" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E23" s="56" t="s">
+      <c r="E23" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="F23" s="56"/>
-      <c r="G23" s="57"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="57"/>
-      <c r="J23" s="57"/>
-      <c r="K23" s="35"/>
-      <c r="L23" s="36"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="36"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="41"/>
+      <c r="L23" s="42"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="42"/>
     </row>
     <row r="24" spans="2:15" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E24" s="58" t="s">
+      <c r="E24" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="F24" s="58"/>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="59"/>
-      <c r="J24" s="59"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="28"/>
-      <c r="M24" s="28"/>
-      <c r="N24" s="28"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="23"/>
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="51"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="52"/>
     </row>
     <row r="25" spans="2:15" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E25" s="58" t="s">
+      <c r="E25" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="F25" s="58"/>
-      <c r="G25" s="59"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="59"/>
-      <c r="J25" s="59"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="28"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="23"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="51"/>
+      <c r="L25" s="52"/>
+      <c r="M25" s="52"/>
+      <c r="N25" s="52"/>
     </row>
     <row r="26" spans="2:15" ht="13.2" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="49" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="26"/>
+      <c r="C26" s="50"/>
       <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
@@ -1380,40 +1412,40 @@
       <c r="N26" s="1"/>
     </row>
     <row r="27" spans="2:15" ht="19.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="31" t="s">
+      <c r="C27" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="D27" s="31" t="s">
+      <c r="D27" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="E27" s="31" t="s">
+      <c r="E27" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="F27" s="31" t="s">
+      <c r="F27" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="G27" s="31" t="s">
+      <c r="G27" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="41" t="s">
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="L27" s="42"/>
-      <c r="M27" s="42"/>
-      <c r="N27" s="43"/>
+      <c r="L27" s="44"/>
+      <c r="M27" s="44"/>
+      <c r="N27" s="45"/>
     </row>
     <row r="28" spans="2:15" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
       <c r="G28" s="5" t="s">
         <v>46</v>
       </c>
@@ -1440,13 +1472,13 @@
       </c>
     </row>
     <row r="29" spans="2:15" ht="15" x14ac:dyDescent="0.2">
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="C29" s="23"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
-      <c r="F29" s="24"/>
+      <c r="C29" s="47"/>
+      <c r="D29" s="47"/>
+      <c r="E29" s="47"/>
+      <c r="F29" s="48"/>
       <c r="G29" s="15"/>
       <c r="H29" s="13">
         <v>0</v>
@@ -1589,24 +1621,48 @@
       <c r="N37" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="58">
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="G22:J22"/>
-    <mergeCell ref="G23:J23"/>
-    <mergeCell ref="G24:J24"/>
-    <mergeCell ref="G25:J25"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
+  <mergeCells count="74">
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G19:J19"/>
+    <mergeCell ref="G17:J17"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="G15:J15"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="G12:J12"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="K16:N16"/>
+    <mergeCell ref="K24:N24"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="F27:F28"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="K20:N20"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="E16:F16"/>
     <mergeCell ref="C27:C28"/>
     <mergeCell ref="K14:N14"/>
     <mergeCell ref="K4:N4"/>
@@ -1623,31 +1679,23 @@
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="F27:F28"/>
-    <mergeCell ref="K21:N21"/>
-    <mergeCell ref="K11:N11"/>
-    <mergeCell ref="K20:N20"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="K22:N22"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="K16:N16"/>
-    <mergeCell ref="K24:N24"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="G22:J22"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="G25:J25"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
